--- a/artfynd/A 58880-2024 artfynd.xlsx
+++ b/artfynd/A 58880-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103049079</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600501.7013748798</v>
+        <v>600502</v>
       </c>
       <c r="R2" t="n">
-        <v>7078933.415296164</v>
+        <v>7078934</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,16 +779,11 @@
         <v>103049086</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600502.9990835714</v>
+        <v>600503</v>
       </c>
       <c r="R3" t="n">
-        <v>7078934.34054148</v>
+        <v>7078934</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -867,19 +847,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
